--- a/ig/DM-JUIN-2026/CodeSystem-TRE-R02-SecteurActivite.xlsx
+++ b/ig/DM-JUIN-2026/CodeSystem-TRE-R02-SecteurActivite.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250523120000</t>
+    <t>20260629120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T12:00:00+01:00</t>
+    <t>2026-06-29T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -457,7 +457,7 @@
     <t>SA40</t>
   </si>
   <si>
-    <t>Secteur privé, praticien hospitalier temps plein</t>
+    <t>Secteur privé, praticien hospitalier</t>
   </si>
   <si>
     <t>SA41</t>
